--- a/data/03_norm.xlsx
+++ b/data/03_norm.xlsx
@@ -3668,11 +3668,11 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>100</v>
+        <v>29.6928</v>
       </c>
     </row>
     <row r="219">
@@ -3683,11 +3683,11 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>100</v>
+        <v>46.5138</v>
       </c>
     </row>
     <row r="220">
@@ -3698,11 +3698,11 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>71.67019999999999</v>
+        <v>17.8831</v>
       </c>
     </row>
     <row r="221">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3728,11 +3728,11 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>64.0592</v>
+        <v>3.2951</v>
       </c>
     </row>
     <row r="223">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3758,11 +3758,11 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>54.5455</v>
+        <v>29.5864</v>
       </c>
     </row>
     <row r="225">
@@ -3773,11 +3773,11 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>17.2304</v>
+        <v>45.6744</v>
       </c>
     </row>
     <row r="226">
@@ -3788,11 +3788,11 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>98.5201</v>
+        <v>99.812</v>
       </c>
     </row>
     <row r="227">
@@ -3803,11 +3803,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>65.0106</v>
+        <v>10.7136</v>
       </c>
     </row>
     <row r="228">
@@ -3818,11 +3818,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>88.9006</v>
+        <v>9.7683</v>
       </c>
     </row>
     <row r="229">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>48.3087</v>
+        <v>13.2025</v>
       </c>
     </row>
     <row r="230">
@@ -3848,11 +3848,11 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>37.1036</v>
+        <v>13.3178</v>
       </c>
     </row>
     <row r="231">
@@ -3863,11 +3863,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>70.8245</v>
+        <v>36.5596</v>
       </c>
     </row>
     <row r="232">
@@ -3878,11 +3878,11 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>28.6469</v>
+        <v>21.3233</v>
       </c>
     </row>
     <row r="233">
@@ -3893,11 +3893,11 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>51.9027</v>
+        <v>36.3176</v>
       </c>
     </row>
     <row r="234">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>47.463</v>
+        <v>36.9638</v>
       </c>
     </row>
     <row r="235">
@@ -3923,11 +3923,11 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>15.5391</v>
+        <v>12.4364</v>
       </c>
     </row>
     <row r="236">
@@ -3938,11 +3938,11 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>58.9852</v>
+        <v>11.0244</v>
       </c>
     </row>
     <row r="237">
@@ -3953,11 +3953,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>72.7273</v>
+        <v>50.9337</v>
       </c>
     </row>
     <row r="238">
@@ -3968,11 +3968,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>31.8182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -3983,11 +3983,11 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>56.871</v>
+        <v>42.1701</v>
       </c>
     </row>
     <row r="240">
@@ -3998,11 +3998,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>48.3087</v>
+        <v>6.3087</v>
       </c>
     </row>
     <row r="241">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>70.40170000000001</v>
+        <v>19.951</v>
       </c>
     </row>
     <row r="242">
@@ -4028,11 +4028,11 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>12.8964</v>
+        <v>17.8767</v>
       </c>
     </row>
     <row r="243">
@@ -4043,11 +4043,11 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>6.9767</v>
+        <v>8.583</v>
       </c>
     </row>
     <row r="244">
@@ -4058,11 +4058,11 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>48.5201</v>
+        <v>19.3577</v>
       </c>
     </row>
     <row r="245">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>17.6533</v>
+        <v>14.4233</v>
       </c>
     </row>
     <row r="246">
@@ -4088,11 +4088,11 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>65.0106</v>
+        <v>3.6349</v>
       </c>
     </row>
     <row r="247">
@@ -4103,11 +4103,11 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>93.7632</v>
+        <v>18.5426</v>
       </c>
     </row>
     <row r="248">
@@ -4118,11 +4118,11 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>6.5539</v>
+        <v>67.5784</v>
       </c>
     </row>
     <row r="249">
@@ -4133,11 +4133,11 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>63.2135</v>
+        <v>37.7108</v>
       </c>
     </row>
     <row r="250">
@@ -4148,11 +4148,11 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>51.797</v>
+        <v>97.108</v>
       </c>
     </row>
     <row r="251">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>52.8541</v>
+        <v>27.0834</v>
       </c>
     </row>
     <row r="252">
@@ -4178,11 +4178,11 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>74.84139999999999</v>
+        <v>54.848</v>
       </c>
     </row>
     <row r="253">
@@ -4193,11 +4193,11 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>10.7822</v>
+        <v>7.7699</v>
       </c>
     </row>
     <row r="254">
@@ -4208,11 +4208,11 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>32.3467</v>
+        <v>26.8801</v>
       </c>
     </row>
     <row r="255">
@@ -4223,11 +4223,11 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>61.8393</v>
+        <v>34.2052</v>
       </c>
     </row>
     <row r="256">
@@ -4238,11 +4238,11 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>47.463</v>
+        <v>2.8836</v>
       </c>
     </row>
     <row r="257">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>0</v>
+        <v>3.5382</v>
       </c>
     </row>
     <row r="258">
@@ -4268,11 +4268,11 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>45.3488</v>
+        <v>25.0375</v>
       </c>
     </row>
     <row r="259">
@@ -4283,11 +4283,11 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>48.7315</v>
+        <v>20.363</v>
       </c>
     </row>
     <row r="260">
@@ -4298,11 +4298,11 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>48.3087</v>
+        <v>25.6984</v>
       </c>
     </row>
     <row r="261">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>59.8309</v>
+        <v>4.9465</v>
       </c>
     </row>
     <row r="262">
@@ -4328,11 +4328,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>74.63</v>
+        <v>57.4644</v>
       </c>
     </row>
     <row r="263">
@@ -4343,11 +4343,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>54.8626</v>
+        <v>40.0746</v>
       </c>
     </row>
     <row r="264">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>54.2283</v>
+        <v>100</v>
       </c>
     </row>
     <row r="265">
@@ -4373,11 +4373,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>85.6237</v>
+        <v>34.7952</v>
       </c>
     </row>
     <row r="266">
@@ -4388,11 +4388,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>86.9979</v>
+        <v>100</v>
       </c>
     </row>
     <row r="267">
@@ -4403,11 +4403,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>89.2178</v>
+        <v>22.3717</v>
       </c>
     </row>
     <row r="268">
@@ -4418,11 +4418,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>35.9408</v>
+        <v>24.655</v>
       </c>
     </row>
     <row r="269">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4448,11 +4448,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>100</v>
+        <v>40.4976</v>
       </c>
     </row>
     <row r="271">
@@ -4463,11 +4463,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>80.23260000000001</v>
+        <v>7.5846</v>
       </c>
     </row>
     <row r="272">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>98.7242</v>
+        <v>100</v>
       </c>
     </row>
     <row r="274">
@@ -4508,11 +4508,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>93.40260000000001</v>
+        <v>76.1099</v>
       </c>
     </row>
     <row r="275">
@@ -4523,11 +4523,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>99.5215</v>
+        <v>100</v>
       </c>
     </row>
     <row r="276">
@@ -4538,11 +4538,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>93.40260000000001</v>
+        <v>64.0592</v>
       </c>
     </row>
     <row r="277">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>75.36450000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="278">
@@ -4568,11 +4568,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>44.8897</v>
+        <v>56.6596</v>
       </c>
     </row>
     <row r="279">
@@ -4583,11 +4583,11 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>44.8897</v>
+        <v>30.2326</v>
       </c>
     </row>
     <row r="280">
@@ -4598,11 +4598,11 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>47.0544</v>
+        <v>98.3087</v>
       </c>
     </row>
     <row r="281">
@@ -4613,11 +4613,11 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>44.8897</v>
+        <v>67.2304</v>
       </c>
     </row>
     <row r="282">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>91.3381</v>
+        <v>91.4376</v>
       </c>
     </row>
     <row r="283">
@@ -4643,11 +4643,11 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>44.8897</v>
+        <v>51.1628</v>
       </c>
     </row>
     <row r="284">
@@ -4658,11 +4658,11 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>44.8897</v>
+        <v>40.4863</v>
       </c>
     </row>
     <row r="285">
@@ -4673,11 +4673,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>44.8897</v>
+        <v>71.3531</v>
       </c>
     </row>
     <row r="286">
@@ -4688,11 +4688,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>44.8897</v>
+        <v>31.1839</v>
       </c>
     </row>
     <row r="287">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>44.8897</v>
+        <v>46.6173</v>
       </c>
     </row>
     <row r="288">
@@ -4718,11 +4718,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>44.8897</v>
+        <v>49.4715</v>
       </c>
     </row>
     <row r="289">
@@ -4733,11 +4733,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>44.8897</v>
+        <v>16.8076</v>
       </c>
     </row>
     <row r="290">
@@ -4748,11 +4748,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>60.3594</v>
       </c>
     </row>
     <row r="291">
@@ -4763,11 +4763,11 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>44.8897</v>
+        <v>81.9239</v>
       </c>
     </row>
     <row r="292">
@@ -4778,11 +4778,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>44.8897</v>
+        <v>35.7294</v>
       </c>
     </row>
     <row r="293">
@@ -4793,11 +4793,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>44.8897</v>
+        <v>58.8795</v>
       </c>
     </row>
     <row r="294">
@@ -4808,10 +4808,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>52.9598</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -4821,11 +4823,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>68.76909999999999</v>
+        <v>70.40170000000001</v>
       </c>
     </row>
     <row r="296">
@@ -4836,11 +4838,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>13.5307</v>
       </c>
     </row>
     <row r="297">
@@ -4851,10 +4853,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>8.4567</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -4864,10 +4868,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>50.3171</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -4877,10 +4883,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>18.0761</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -4890,10 +4898,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>63.1078</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -4903,10 +4913,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>94.8203</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -4916,11 +4928,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>70.78870000000001</v>
+        <v>15.5391</v>
       </c>
     </row>
     <row r="303">
@@ -4931,11 +4943,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>67.1095</v>
+        <v>67.4419</v>
       </c>
     </row>
     <row r="304">
@@ -4946,11 +4958,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>67.1095</v>
+        <v>52.7484</v>
       </c>
     </row>
     <row r="305">
@@ -4961,11 +4973,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>67.1095</v>
+        <v>54.1226</v>
       </c>
     </row>
     <row r="306">
@@ -4976,11 +4988,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>62.4601</v>
+        <v>75.6871</v>
       </c>
     </row>
     <row r="307">
@@ -4991,11 +5003,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>67.1095</v>
+        <v>10.7822</v>
       </c>
     </row>
     <row r="308">
@@ -5006,11 +5018,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>67.1095</v>
+        <v>33.2981</v>
       </c>
     </row>
     <row r="309">
@@ -5021,11 +5033,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>67.1095</v>
+        <v>70.40170000000001</v>
       </c>
     </row>
     <row r="310">
@@ -5036,11 +5048,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>67.1095</v>
+        <v>51.797</v>
       </c>
     </row>
     <row r="311">
@@ -5051,11 +5063,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>67.1095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -5066,11 +5078,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>78.4165</v>
+        <v>49.6829</v>
       </c>
     </row>
     <row r="313">
@@ -5081,11 +5093,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>56.5474</v>
+        <v>52.7484</v>
       </c>
     </row>
     <row r="314">
@@ -5096,11 +5108,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>67.1095</v>
+        <v>50.9514</v>
       </c>
     </row>
     <row r="315">
@@ -5111,11 +5123,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>67.33459999999999</v>
+        <v>59.8309</v>
       </c>
     </row>
     <row r="316">
@@ -5126,11 +5138,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>79.0698</v>
       </c>
     </row>
     <row r="317">
@@ -5141,11 +5153,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>58.351</v>
       </c>
     </row>
     <row r="318">
@@ -5156,11 +5168,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2.136</v>
+        <v>56.9767</v>
       </c>
     </row>
     <row r="319">
@@ -5171,11 +5183,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>88.6892</v>
       </c>
     </row>
     <row r="320">
@@ -5186,11 +5198,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>89.64060000000001</v>
       </c>
     </row>
     <row r="321">
@@ -5201,10 +5213,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>91.22620000000001</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5214,10 +5228,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>39.2178</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5227,11 +5243,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>81.09</v>
+        <v>100</v>
       </c>
     </row>
     <row r="324">
@@ -5242,11 +5258,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>21.3456</v>
+        <v>100</v>
       </c>
     </row>
     <row r="325">
@@ -5257,10 +5273,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>femicide</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr"/>
+          <t>elec_access_tot</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>76.4271</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5270,11 +5288,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>15.2601</v>
+        <v>100</v>
       </c>
     </row>
     <row r="327">
@@ -5285,11 +5303,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>9.039300000000001</v>
+        <v>98.7242</v>
       </c>
     </row>
     <row r="328">
@@ -5300,11 +5318,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>15.2601</v>
+        <v>93.40260000000001</v>
       </c>
     </row>
     <row r="329">
@@ -5315,11 +5333,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>26.5767</v>
+        <v>99.5215</v>
       </c>
     </row>
     <row r="330">
@@ -5330,11 +5348,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>1.8623</v>
+        <v>93.40260000000001</v>
       </c>
     </row>
     <row r="331">
@@ -5345,11 +5363,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>23.5619</v>
+        <v>75.36450000000001</v>
       </c>
     </row>
     <row r="332">
@@ -5360,11 +5378,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>44.652</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="333">
@@ -5375,11 +5393,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>17.246</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="334">
@@ -5390,11 +5408,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>53.5045</v>
+        <v>47.0544</v>
       </c>
     </row>
     <row r="335">
@@ -5405,11 +5423,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>37.177</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="336">
@@ -5420,11 +5438,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>23.3561</v>
+        <v>91.3381</v>
       </c>
     </row>
     <row r="337">
@@ -5435,11 +5453,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>14.9011</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="338">
@@ -5450,11 +5468,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>19.155</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="339">
@@ -5465,11 +5483,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>47.8243</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="340">
@@ -5480,11 +5498,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>48.9187</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="341">
@@ -5495,11 +5513,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>6.6405</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="342">
@@ -5510,11 +5528,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>25.9938</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="343">
@@ -5525,11 +5543,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>20.0295</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="344">
@@ -5540,11 +5558,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>19.166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -5555,11 +5573,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>23.7323</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="346">
@@ -5570,11 +5588,11 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>6.039</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="347">
@@ -5585,11 +5603,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>35.9948</v>
+        <v>44.8897</v>
       </c>
     </row>
     <row r="348">
@@ -5600,12 +5618,10 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C348" t="n">
-        <v>36.988</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -5615,11 +5631,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>20.5178</v>
+        <v>68.76909999999999</v>
       </c>
     </row>
     <row r="350">
@@ -5630,11 +5646,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>59.2291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -5645,12 +5661,10 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C351" t="n">
-        <v>15.2252</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -5660,12 +5674,10 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C352" t="n">
-        <v>48.0399</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -5675,12 +5687,10 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C353" t="n">
-        <v>8.795299999999999</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -5690,12 +5700,10 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C354" t="n">
-        <v>100</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -5705,12 +5713,10 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C355" t="n">
-        <v>100</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -5720,11 +5726,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>43.7181</v>
+        <v>70.78870000000001</v>
       </c>
     </row>
     <row r="357">
@@ -5735,11 +5741,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>26.9156</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="358">
@@ -5750,11 +5756,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>3.6961</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="359">
@@ -5765,11 +5771,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>13.3064</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="360">
@@ -5780,11 +5786,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>20.352</v>
+        <v>62.4601</v>
       </c>
     </row>
     <row r="361">
@@ -5795,11 +5801,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>43.7262</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="362">
@@ -5810,11 +5816,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>48.8416</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="363">
@@ -5825,11 +5831,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>15.1502</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="364">
@@ -5840,11 +5846,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>32.4376</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="365">
@@ -5855,11 +5861,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>93.5652</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="366">
@@ -5870,11 +5876,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>13.4155</v>
+        <v>78.4165</v>
       </c>
     </row>
     <row r="367">
@@ -5885,11 +5891,11 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>21.6964</v>
+        <v>56.5474</v>
       </c>
     </row>
     <row r="368">
@@ -5900,11 +5906,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>54.6191</v>
+        <v>67.1095</v>
       </c>
     </row>
     <row r="369">
@@ -5915,11 +5921,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>22.6865</v>
+        <v>67.33459999999999</v>
       </c>
     </row>
     <row r="370">
@@ -5930,11 +5936,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>36.6838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -5945,11 +5951,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>62.5209</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -5960,11 +5966,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>42.8028</v>
+        <v>2.136</v>
       </c>
     </row>
     <row r="373">
@@ -5975,11 +5981,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>13.6788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -5990,7 +5996,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6005,12 +6011,10 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>15.4025</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -6020,12 +6024,10 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C376" t="n">
-        <v>19.4914</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6035,11 +6037,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>19.5734</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="378">
@@ -6050,11 +6052,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>7.1427</v>
+        <v>21.3456</v>
       </c>
     </row>
     <row r="379">
@@ -6065,12 +6067,10 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>15.4025</v>
-      </c>
+          <t>femicide</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>88.41670000000001</v>
+        <v>88.6067</v>
       </c>
     </row>
     <row r="489">
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>91.02290000000001</v>
+        <v>91.2171</v>
       </c>
     </row>
     <row r="490">
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>81.6486</v>
+        <v>81.8276</v>
       </c>
     </row>
     <row r="491">
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>71.35250000000001</v>
+        <v>71.5149</v>
       </c>
     </row>
     <row r="492">
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>19.6369</v>
+        <v>19.7158</v>
       </c>
     </row>
     <row r="493">
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>82.1377</v>
+        <v>82.3175</v>
       </c>
     </row>
     <row r="494">
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>43.6454</v>
+        <v>43.7631</v>
       </c>
     </row>
     <row r="495">
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>29.8189</v>
+        <v>29.9248</v>
       </c>
     </row>
     <row r="496">
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="C496" t="n">
-        <v>73.6961</v>
+        <v>73.78489999999999</v>
       </c>
     </row>
     <row r="497">
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="C497" t="n">
-        <v>35.7394</v>
+        <v>35.8443</v>
       </c>
     </row>
     <row r="498">
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="C498" t="n">
-        <v>62.8722</v>
+        <v>63.0999</v>
       </c>
     </row>
     <row r="499">
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="C499" t="n">
-        <v>44.5882</v>
+        <v>44.7074</v>
       </c>
     </row>
     <row r="500">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>32.2308</v>
+        <v>32.0118</v>
       </c>
     </row>
     <row r="501">
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>61.4209</v>
+        <v>61.5672</v>
       </c>
     </row>
     <row r="502">
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>15.6487</v>
+        <v>15.7211</v>
       </c>
     </row>
     <row r="503">
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>34.2021</v>
+        <v>34.324</v>
       </c>
     </row>
     <row r="504">
@@ -7944,7 +7944,7 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>60.1239</v>
+        <v>60.2682</v>
       </c>
     </row>
     <row r="505">
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>18.6107</v>
+        <v>18.5474</v>
       </c>
     </row>
     <row r="506">
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>66.9251</v>
+        <v>67.0796</v>
       </c>
     </row>
     <row r="507">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>47.9948</v>
+        <v>48.2423</v>
       </c>
     </row>
     <row r="508">
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>36.1724</v>
+        <v>36.278</v>
       </c>
     </row>
     <row r="509">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>34.6945</v>
+        <v>38.8236</v>
       </c>
     </row>
     <row r="510">
@@ -8034,7 +8034,7 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>70.4152</v>
+        <v>70.027</v>
       </c>
     </row>
     <row r="511">
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>51.153</v>
+        <v>51.2828</v>
       </c>
     </row>
     <row r="512">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>2.9046</v>
+        <v>2.9564</v>
       </c>
     </row>
     <row r="513">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>28.0551</v>
+        <v>28.3873</v>
       </c>
     </row>
     <row r="514">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>58.5799</v>
+        <v>58.5693</v>
       </c>
     </row>
     <row r="515">
@@ -8109,7 +8109,7 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>14.7702</v>
+        <v>14.8338</v>
       </c>
     </row>
     <row r="516">
@@ -8124,7 +8124,7 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>88.3172</v>
+        <v>87.532</v>
       </c>
     </row>
     <row r="517">
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>94.8896</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="518">
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="C518" t="n">
-        <v>1.1058</v>
+        <v>1.0555</v>
       </c>
     </row>
     <row r="519">
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>62.0123</v>
+        <v>62.1596</v>
       </c>
     </row>
     <row r="520">
@@ -8184,7 +8184,7 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>13.3367</v>
+        <v>13.3582</v>
       </c>
     </row>
     <row r="521">
@@ -8199,7 +8199,7 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>33.9344</v>
+        <v>34.0363</v>
       </c>
     </row>
     <row r="522">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>56.7648</v>
+        <v>56.8836</v>
       </c>
     </row>
     <row r="523">
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>15.4151</v>
+        <v>15.4872</v>
       </c>
     </row>
     <row r="524">
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="C524" t="n">
-        <v>12.6415</v>
+        <v>12.7176</v>
       </c>
     </row>
     <row r="525">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="C525" t="n">
-        <v>37.8644</v>
+        <v>38.5682</v>
       </c>
     </row>
     <row r="526">
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>10.6124</v>
+        <v>10.6767</v>
       </c>
     </row>
     <row r="527">
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="C528" t="n">
-        <v>42.0423</v>
+        <v>42.1574</v>
       </c>
     </row>
     <row r="529">
@@ -8319,7 +8319,7 @@
         </is>
       </c>
       <c r="C529" t="n">
-        <v>33.7933</v>
+        <v>33.895</v>
       </c>
     </row>
     <row r="530">
@@ -8334,7 +8334,7 @@
         </is>
       </c>
       <c r="C530" t="n">
-        <v>41.9969</v>
+        <v>42.1119</v>
       </c>
     </row>
     <row r="531">
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>53.0644</v>
+        <v>53.1763</v>
       </c>
     </row>
     <row r="532">
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="C532" t="n">
-        <v>93.3888</v>
+        <v>93.6571</v>
       </c>
     </row>
     <row r="533">
@@ -8379,7 +8379,7 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>30.9774</v>
+        <v>31.7728</v>
       </c>
     </row>
     <row r="534">
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="C534" t="n">
-        <v>75.09050000000001</v>
+        <v>75.2432</v>
       </c>
     </row>
     <row r="535">
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="C535" t="n">
-        <v>75.4016</v>
+        <v>75.58880000000001</v>
       </c>
     </row>
     <row r="536">
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="C536" t="n">
-        <v>84.1632</v>
+        <v>84.3463</v>
       </c>
     </row>
     <row r="537">
@@ -8439,7 +8439,7 @@
         </is>
       </c>
       <c r="C537" t="n">
-        <v>39.9608</v>
+        <v>40.7513</v>
       </c>
     </row>
     <row r="538">
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="C538" t="n">
-        <v>15.8646</v>
+        <v>15.9785</v>
       </c>
     </row>
     <row r="539">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="C541" t="n">
-        <v>54.7381</v>
+        <v>54.9952</v>
       </c>
     </row>
     <row r="542">
@@ -26515,7 +26515,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elec_access_tot</t>
+          <t>domestic_credit_private</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>5.4</v>
+        <v>3.967826</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>54.708523</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -26547,65 +26547,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>femicide</t>
+          <t>elec_access_tot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.464294</v>
+        <v>5.4</v>
       </c>
       <c r="E7" t="n">
-        <v>6.309057</v>
+        <v>100</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
         <v>54</v>
       </c>
       <c r="J7" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>firm_foreign_owned</t>
+          <t>femicide</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.364913</v>
+        <v>0.464294</v>
       </c>
       <c r="E8" t="n">
-        <v>46.710372</v>
+        <v>6.309057</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
         <v>54</v>
       </c>
       <c r="J8" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="9">
@@ -26690,13 +26690,13 @@
         <v>7.052623</v>
       </c>
       <c r="E11" t="n">
-        <v>10.133788</v>
+        <v>10.12882</v>
       </c>
       <c r="F11" t="n">
         <v>7.052623</v>
       </c>
       <c r="G11" t="n">
-        <v>10.133788</v>
+        <v>10.12882</v>
       </c>
       <c r="H11" t="n">
         <v>54</v>
